--- a/SPEC MyBook Pro L3.xlsx
+++ b/SPEC MyBook Pro L3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Downloads\Spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Desktop\axioo_b2g\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECBC8A0-5E3E-46C8-8F84-4224B7B49AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2216817B-4A46-4FE9-8479-28D360B7D51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,12 +53,150 @@
     <t>Intel® Core™  i3-1215U Processor (6 Cores, 8 Threads, TDP:15W)</t>
   </si>
   <si>
+    <t>Code Name</t>
+  </si>
+  <si>
+    <t>Intel® Alder Lake</t>
+  </si>
+  <si>
+    <t>Graphics Controller</t>
+  </si>
+  <si>
+    <t>Intel® UHD Graphics</t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>14" inch IPS (16:9)</t>
+  </si>
+  <si>
+    <t>Display  / Resolution</t>
+  </si>
+  <si>
+    <t>FHD 1920x1080</t>
+  </si>
+  <si>
+    <t>Memory RAM</t>
+  </si>
+  <si>
+    <t>2x SODIMM DDR4 Dual Channel Up to 64GB</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>1x M.2 NVMe 2280 SSD, support PCIe 4.0 x4</t>
+  </si>
+  <si>
+    <t>Camera Front</t>
+  </si>
+  <si>
+    <t>1.0 Mpx</t>
+  </si>
+  <si>
+    <t>Sound System</t>
+  </si>
+  <si>
+    <t>HD Audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built-in Microphone </t>
+  </si>
+  <si>
+    <t>I/O Ports</t>
+  </si>
+  <si>
+    <t>1 x USB 3.1 Type C port</t>
+  </si>
+  <si>
+    <t>1 x USB 2.0 Type A port (childboard side)</t>
+  </si>
+  <si>
+    <t>1 x USB 3.1 ports</t>
+  </si>
+  <si>
+    <t>1 x 3.5mm Audio Combo Jack</t>
+  </si>
+  <si>
+    <t>1 x GigaBit LAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x HDMI output port </t>
+  </si>
+  <si>
+    <t>1 x MicroSD port</t>
+  </si>
+  <si>
+    <t>1 x DC-in jack port</t>
+  </si>
+  <si>
+    <t>Power Management</t>
+  </si>
+  <si>
+    <t>AC Adapter 19.0V/2.37A, 45W</t>
+  </si>
+  <si>
+    <t>Embedded 3 cells Lithium-Ion battery pack,11.4V,36Wh,3175mAh</t>
+  </si>
+  <si>
+    <t>Connection</t>
+  </si>
+  <si>
+    <t>Intel® Wireless-AC 9462 802.11 ac/b/g/n network adapter</t>
+  </si>
+  <si>
+    <t>Bluetooth 5.1</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Kensington Lock</t>
+  </si>
+  <si>
+    <t>TPM 2.0</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x Speakers  </t>
+  </si>
+  <si>
+    <t>Bios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insyde BIOS </t>
+  </si>
+  <si>
+    <t>O.S</t>
+  </si>
+  <si>
+    <t>Windows® 11 (64-bit)</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>324(W) x 220(D) x 19(H)mm</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>1300g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyBook Pro L3 </t>
+  </si>
+  <si>
     <r>
       <t>Performance Cores:</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -73,7 +211,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -81,144 +219,6 @@
       </rPr>
       <t xml:space="preserve"> 4 Cores, 4 Threads, 0.9 GHz Base, 3.3 GHz Turbo</t>
     </r>
-  </si>
-  <si>
-    <t>Code Name</t>
-  </si>
-  <si>
-    <t>Intel® Alder Lake</t>
-  </si>
-  <si>
-    <t>Graphics Controller</t>
-  </si>
-  <si>
-    <t>Intel® UHD Graphics</t>
-  </si>
-  <si>
-    <t>LCD</t>
-  </si>
-  <si>
-    <t>14" inch IPS (16:9)</t>
-  </si>
-  <si>
-    <t>Display  / Resolution</t>
-  </si>
-  <si>
-    <t>FHD 1920x1080</t>
-  </si>
-  <si>
-    <t>Memory RAM</t>
-  </si>
-  <si>
-    <t>2x SODIMM DDR4 Dual Channel Up to 64GB</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>1x M.2 NVMe 2280 SSD, support PCIe 4.0 x4</t>
-  </si>
-  <si>
-    <t>Camera Front</t>
-  </si>
-  <si>
-    <t>1.0 Mpx</t>
-  </si>
-  <si>
-    <t>Sound System</t>
-  </si>
-  <si>
-    <t>HD Audio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built-in Microphone </t>
-  </si>
-  <si>
-    <t>I/O Ports</t>
-  </si>
-  <si>
-    <t>1 x USB 3.1 Type C port</t>
-  </si>
-  <si>
-    <t>1 x USB 2.0 Type A port (childboard side)</t>
-  </si>
-  <si>
-    <t>1 x USB 3.1 ports</t>
-  </si>
-  <si>
-    <t>1 x 3.5mm Audio Combo Jack</t>
-  </si>
-  <si>
-    <t>1 x GigaBit LAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x HDMI output port </t>
-  </si>
-  <si>
-    <t>1 x MicroSD port</t>
-  </si>
-  <si>
-    <t>1 x DC-in jack port</t>
-  </si>
-  <si>
-    <t>Power Management</t>
-  </si>
-  <si>
-    <t>AC Adapter 19.0V/2.37A, 45W</t>
-  </si>
-  <si>
-    <t>Embedded 3 cells Lithium-Ion battery pack,11.4V,36Wh,3175mAh</t>
-  </si>
-  <si>
-    <t>Connection</t>
-  </si>
-  <si>
-    <t>Intel® Wireless-AC 9462 802.11 ac/b/g/n network adapter</t>
-  </si>
-  <si>
-    <t>Bluetooth 5.1</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Kensington Lock</t>
-  </si>
-  <si>
-    <t>TPM 2.0</t>
-  </si>
-  <si>
-    <t>Speaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x Speakers  </t>
-  </si>
-  <si>
-    <t>Bios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insyde BIOS </t>
-  </si>
-  <si>
-    <t>O.S</t>
-  </si>
-  <si>
-    <t>Windows® 11 (64-bit)</t>
-  </si>
-  <si>
-    <t>Dimension</t>
-  </si>
-  <si>
-    <t>324(W) x 220(D) x 19(H)mm</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>1300g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyBook Pro L3 </t>
   </si>
 </sst>
 </file>
@@ -234,43 +234,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -286,23 +253,58 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -403,132 +405,133 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -838,395 +841,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
-    <col min="2" max="2" width="88.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="74.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="8.88671875" style="2"/>
+    <col min="6" max="6" width="21.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="2"/>
+    <col min="10" max="10" width="21.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="74.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="32"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="37"/>
+      <c r="B4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="38"/>
+      <c r="B5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="41"/>
-      <c r="G3" s="25"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="45"/>
-      <c r="B4" s="27" t="s">
+      <c r="F5" s="8"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="32"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="44"/>
-      <c r="B5" s="28" t="s">
+      <c r="B6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="32"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="22" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="35"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="22" t="s">
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="23" t="s">
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="24" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="32"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="22" t="s">
+      <c r="F10" s="8"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="33"/>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="22" t="s">
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="33"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="22" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="32"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="42" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="40"/>
+      <c r="B14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="41"/>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="42"/>
-      <c r="B14" s="15" t="s">
+      <c r="B15" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="32"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="42" t="s">
+      <c r="F15" s="3"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="40"/>
+      <c r="B16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="40"/>
+      <c r="B17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="32"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="42"/>
-      <c r="B16" s="14" t="s">
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="40"/>
+      <c r="B18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="42"/>
-      <c r="B17" s="14" t="s">
+      <c r="F18" s="3"/>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="40"/>
+      <c r="B19" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="41"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="42"/>
-      <c r="B18" s="16" t="s">
+      <c r="F19" s="3"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="40"/>
+      <c r="B20" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="38"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="42"/>
-      <c r="B19" s="16" t="s">
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="40"/>
+      <c r="B21" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="32"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="42"/>
-      <c r="B20" s="19" t="s">
+      <c r="F21" s="3"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="40"/>
+      <c r="B22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="41"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="42"/>
-      <c r="B21" s="19" t="s">
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="41"/>
-      <c r="G21" s="32"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="42"/>
-      <c r="B22" s="14" t="s">
+      <c r="B23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="41"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="43" t="s">
+      <c r="F23" s="3"/>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="38"/>
+      <c r="B24" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="41"/>
-      <c r="G23" s="31"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="44"/>
-      <c r="B24" s="16" t="s">
+      <c r="B25" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="41"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="42" t="s">
+      <c r="F25" s="8"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="40"/>
+      <c r="B26" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="F26" s="3"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="33"/>
-      <c r="G25" s="32"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="42"/>
-      <c r="B26" s="16" t="s">
+      <c r="B27" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="41"/>
-      <c r="G26" s="32"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="42" t="s">
+      <c r="F27" s="3"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="40"/>
+      <c r="B28" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="F28" s="8"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="41"/>
-      <c r="G27" s="32"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="42"/>
-      <c r="B28" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="33"/>
-      <c r="G28" s="32"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="22" t="s">
+      <c r="F29" s="8"/>
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="33"/>
-      <c r="G29" s="39"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="22" t="s">
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B31" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="F30" s="33"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="22" t="s">
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" spans="1:7" ht="13.2">
+      <c r="A32" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B32" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="33"/>
-    </row>
-    <row r="32" spans="1:7" ht="15">
-      <c r="A32" s="22" t="s">
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B33" s="29" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="31"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="2"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="31"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="21"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="21"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
+      <c r="A38" s="43"/>
+      <c r="B38" s="32"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="33"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="30"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="30"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="30"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
+      <c r="A43" s="44"/>
+      <c r="B43" s="34"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="10"/>
-      <c r="B44" s="7"/>
+      <c r="A44" s="45"/>
+      <c r="B44" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F20"/>
+    <mergeCell ref="F21:F22"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A22"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F20"/>
-    <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F24"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F1C94A586F6A64AA956C7CA2AB05C9B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7b39dff72ebd7b03cdb9d3443bb53f9a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f82bd302-08e5-41cf-ac7e-929bc680f927" xmlns:ns3="189b1353-a086-487c-981c-f6344e352306" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6783e78daab35a5ff41903a679763a9d" ns2:_="" ns3:_="">
     <xsd:import namespace="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
@@ -1461,10 +1447,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0F10085-313F-4157-AF99-4E3CECE8CC2D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E940F3A9-DBDD-442C-8147-42EDC0872D71}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
+    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1481,20 +1498,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E940F3A9-DBDD-442C-8147-42EDC0872D71}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0F10085-313F-4157-AF99-4E3CECE8CC2D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
-    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>